--- a/Assets/AddressableResource/Data/Excels/TowerWeaponJewelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/TowerWeaponJewelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DB8063-6DDB-4FB6-AAD2-60BD579B79F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21E10A6-5F50-4DEB-A5E8-1360F392A909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,15 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="37">
-  <si>
-    <t>up</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>requireCoin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="33">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>addCoin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Normal</t>
   </si>
   <si>
@@ -123,14 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이건 따로 빼자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공통으로 쓸 예쩡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Atk</t>
   </si>
   <si>
@@ -167,6 +147,10 @@
   </si>
   <si>
     <t>weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grade</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -268,13 +252,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -582,66 +566,51 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Q145"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="18.875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="7" customWidth="1"/>
-    <col min="6" max="8" width="19" style="7" customWidth="1"/>
-    <col min="9" max="9" width="19" style="3" customWidth="1"/>
-    <col min="10" max="10" width="18.375" style="3" customWidth="1"/>
-    <col min="11" max="16" width="17.625" style="3"/>
-    <col min="18" max="16384" width="17.625" style="3"/>
+    <col min="1" max="4" width="18.875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="19" style="6" customWidth="1"/>
+    <col min="7" max="12" width="17.625" style="3"/>
+    <col min="14" max="16384" width="17.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="K1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -650,222 +619,202 @@
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="1">
+        <v>16</v>
+      </c>
+      <c r="H2" s="7">
+        <f t="shared" ref="H2:H43" si="0">D2/I2</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I2" s="3">
+        <f>SUM($D$2:$D$8)</f>
+        <v>6</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4">
-        <v>1500</v>
-      </c>
-      <c r="K2" s="3">
-        <v>100</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I8" si="1">SUM($D$2:$D$8)</f>
+        <v>6</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="1">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3">
-        <v>20</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="1">
-        <v>4</v>
-      </c>
-      <c r="J3" s="4">
-        <v>3150</v>
-      </c>
-      <c r="K3" s="3">
-        <v>210</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="E4" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>40</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="1">
-        <v>3</v>
-      </c>
-      <c r="J4" s="4">
-        <v>6620</v>
-      </c>
-      <c r="K4" s="3">
-        <v>450</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>80</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="4">
-        <v>13910</v>
-      </c>
-      <c r="K5" s="3">
-        <v>950</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>160</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="4">
-        <v>29220</v>
-      </c>
-      <c r="K6" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>320</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4">
-        <v>61370</v>
-      </c>
-      <c r="K7" s="3">
-        <v>4200</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -874,2433 +823,2009 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="1">
-        <v>5</v>
-      </c>
-      <c r="J8" s="4">
-        <v>1500</v>
-      </c>
-      <c r="K8" s="3">
-        <v>100</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3">
-        <v>5</v>
+        <f>F2/2</f>
+        <v>8</v>
       </c>
       <c r="F9" s="3">
-        <v>20</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="1">
-        <v>4</v>
-      </c>
-      <c r="J9" s="4">
-        <v>3150</v>
-      </c>
-      <c r="K9" s="3">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <f>F2*2</f>
+        <v>32</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="I9" s="3">
+        <f>SUM($D$9:$D$15)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="1">
-        <v>3</v>
-      </c>
       <c r="E10" s="3">
-        <v>10</v>
+        <f t="shared" ref="E10:E43" si="2">F3/2</f>
+        <v>8</v>
       </c>
       <c r="F10" s="3">
-        <v>40</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="1">
-        <v>3</v>
-      </c>
-      <c r="J10" s="4">
-        <v>6620</v>
-      </c>
-      <c r="K10" s="3">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <f t="shared" ref="F10:F43" si="3">F3*2</f>
+        <v>32</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="0"/>
+        <v>0.31034482758620691</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" ref="I10:I15" si="4">SUM($D$9:$D$15)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
       <c r="E11" s="3">
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="F11" s="3">
-        <v>80</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="1">
-        <v>2</v>
-      </c>
-      <c r="J11" s="4">
-        <v>13910</v>
-      </c>
-      <c r="K11" s="3">
-        <v>950</v>
-      </c>
-      <c r="N11" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="0"/>
+        <v>0.31034482758620691</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="J11" s="1">
         <v>5</v>
       </c>
-      <c r="O11" s="4">
+      <c r="K11" s="4">
         <v>1500</v>
       </c>
-      <c r="P11" s="3">
+      <c r="L11" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E12" s="3">
-        <v>40</v>
+        <f t="shared" si="2"/>
+        <v>0.01</v>
       </c>
       <c r="F12" s="3">
-        <v>160</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="J12" s="4">
-        <v>29220</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N12" s="1">
+        <f>F5*2</f>
+        <v>0.04</v>
+      </c>
+      <c r="H12" s="7">
+        <f t="shared" si="0"/>
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="J12" s="1">
         <v>4</v>
       </c>
-      <c r="O12" s="4">
+      <c r="K12" s="4">
         <v>3150</v>
       </c>
-      <c r="P12" s="3">
+      <c r="L12" s="3">
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="3">
-        <v>80</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="F13" s="3">
-        <v>320</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <v>61370</v>
-      </c>
-      <c r="K13" s="3">
-        <v>4200</v>
-      </c>
-      <c r="N13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="J13" s="1">
         <v>3</v>
       </c>
-      <c r="O13" s="4">
+      <c r="K13" s="4">
         <v>6620</v>
       </c>
-      <c r="P13" s="3">
+      <c r="L13" s="3">
         <v>450</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="1">
-        <v>5</v>
-      </c>
-      <c r="J14" s="4">
-        <v>1500</v>
-      </c>
-      <c r="K14" s="3">
-        <v>100</v>
-      </c>
-      <c r="N14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="J14" s="1">
         <v>2</v>
       </c>
-      <c r="O14" s="4">
+      <c r="K14" s="4">
         <v>13910</v>
       </c>
-      <c r="P14" s="3">
+      <c r="L14" s="3">
         <v>950</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>20</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="1">
-        <v>4</v>
-      </c>
-      <c r="J15" s="4">
-        <v>3150</v>
-      </c>
-      <c r="K15" s="3">
-        <v>210</v>
-      </c>
-      <c r="N15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="J15" s="1">
         <v>1</v>
       </c>
-      <c r="O15" s="4">
+      <c r="K15" s="4">
         <v>29220</v>
       </c>
-      <c r="P15" s="3">
+      <c r="L15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="0"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="I16" s="3">
+        <f>SUM($D$16:$D$22)</f>
         <v>11</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3">
-        <v>10</v>
-      </c>
-      <c r="F16" s="3">
-        <v>40</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="1">
-        <v>3</v>
-      </c>
-      <c r="J16" s="4">
-        <v>6620</v>
-      </c>
-      <c r="K16" s="3">
-        <v>450</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4">
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
         <v>61370</v>
       </c>
-      <c r="P16" s="3">
+      <c r="L16" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>16</v>
       </c>
       <c r="F17" s="3">
-        <v>80</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="1">
-        <v>2</v>
-      </c>
-      <c r="J17" s="4">
-        <v>13910</v>
-      </c>
-      <c r="K17" s="3">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="0"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" ref="I17:I22" si="5">SUM($D$16:$D$22)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>6</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="0"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>40</v>
-      </c>
-      <c r="F18" s="3">
-        <v>160</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="1">
-        <v>1</v>
-      </c>
-      <c r="J18" s="4">
-        <v>29220</v>
+      <c r="J18" s="3">
+        <v>0</v>
       </c>
       <c r="K18" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="2"/>
+        <v>0.02</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="3"/>
+        <v>0.08</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="0"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>80</v>
-      </c>
-      <c r="F19" s="3">
-        <v>320</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4">
-        <v>61370</v>
+      <c r="J19" s="3">
+        <v>5</v>
       </c>
       <c r="K19" s="3">
-        <v>4200</v>
-      </c>
-      <c r="N19" s="3">
-        <v>5</v>
-      </c>
-      <c r="O19" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="3">
+        <v>4</v>
+      </c>
+      <c r="H20" s="7">
+        <f t="shared" si="0"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="J20" s="3">
         <v>10</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="1">
-        <v>5</v>
-      </c>
-      <c r="J20" s="4">
-        <v>1500</v>
-      </c>
       <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>10</v>
-      </c>
-      <c r="O20" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="J21" s="3">
         <v>20</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="1">
-        <v>4</v>
-      </c>
-      <c r="J21" s="4">
-        <v>3150</v>
-      </c>
       <c r="K21" s="3">
-        <v>210</v>
-      </c>
-      <c r="N21" s="3">
-        <v>20</v>
-      </c>
-      <c r="O21" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>10</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="J22" s="3">
         <v>40</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="1">
-        <v>3</v>
-      </c>
-      <c r="J22" s="4">
-        <v>6620</v>
-      </c>
       <c r="K22" s="3">
-        <v>450</v>
-      </c>
-      <c r="N22" s="3">
-        <v>40</v>
-      </c>
-      <c r="O22" s="3">
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E23" s="3">
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>32</v>
       </c>
       <c r="F23" s="3">
+        <f t="shared" si="3"/>
+        <v>128</v>
+      </c>
+      <c r="H23" s="7">
+        <f t="shared" si="0"/>
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="I23" s="3">
+        <f>SUM($D$23:$D$29)</f>
+        <v>29</v>
+      </c>
+      <c r="J23" s="3">
         <v>80</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="1">
-        <v>2</v>
-      </c>
-      <c r="J23" s="4">
-        <v>13910</v>
-      </c>
       <c r="K23" s="3">
-        <v>950</v>
-      </c>
-      <c r="N23" s="3">
-        <v>80</v>
-      </c>
-      <c r="O23" s="3">
         <v>320</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D24" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E24" s="3">
-        <v>40</v>
+        <f t="shared" si="2"/>
+        <v>32</v>
       </c>
       <c r="F24" s="3">
-        <v>160</v>
-      </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="1">
-        <v>1</v>
-      </c>
-      <c r="J24" s="4">
-        <v>29220</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>128</v>
+      </c>
+      <c r="H24" s="7">
+        <f t="shared" si="0"/>
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" ref="I24:I29" si="6">SUM($D$23:$D$29)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D25" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" s="3">
-        <v>80</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="F25" s="3">
-        <v>320</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4">
-        <v>61370</v>
-      </c>
-      <c r="K25" s="3">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="H25" s="7">
+        <f t="shared" si="0"/>
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>0.04</v>
       </c>
       <c r="F26" s="3">
-        <v>10</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="1">
-        <v>5</v>
-      </c>
-      <c r="J26" s="4">
-        <v>1500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>0.16</v>
+      </c>
+      <c r="H26" s="7">
+        <f t="shared" si="0"/>
+        <v>0.20689655172413793</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27" s="3">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="F27" s="3">
-        <v>20</v>
-      </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="1">
-        <v>4</v>
-      </c>
-      <c r="J27" s="4">
-        <v>3150</v>
-      </c>
-      <c r="K27" s="3">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="H27" s="7">
+        <f t="shared" si="0"/>
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="3">
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="F28" s="3">
-        <v>40</v>
-      </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="1">
-        <v>3</v>
-      </c>
-      <c r="J28" s="4">
-        <v>6620</v>
-      </c>
-      <c r="K28" s="3">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="H28" s="7">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>80</v>
-      </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="1">
-        <v>2</v>
-      </c>
-      <c r="J29" s="4">
-        <v>13910</v>
-      </c>
-      <c r="K29" s="3">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E30" s="3">
-        <v>40</v>
+        <f t="shared" si="2"/>
+        <v>64</v>
       </c>
       <c r="F30" s="3">
-        <v>160</v>
-      </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="1">
-        <v>1</v>
-      </c>
-      <c r="J30" s="4">
-        <v>29220</v>
-      </c>
-      <c r="K30" s="3">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>256</v>
+      </c>
+      <c r="H30" s="7">
+        <f t="shared" si="0"/>
+        <v>0.22641509433962265</v>
+      </c>
+      <c r="I30" s="3">
+        <f>SUM($D$30:$D$36)</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D31" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E31" s="3">
-        <v>80</v>
+        <f t="shared" si="2"/>
+        <v>64</v>
       </c>
       <c r="F31" s="3">
-        <v>320</v>
-      </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
-      <c r="J31" s="4">
-        <v>61370</v>
-      </c>
-      <c r="K31" s="3">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>256</v>
+      </c>
+      <c r="H31" s="7">
+        <f t="shared" si="0"/>
+        <v>0.15094339622641509</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" ref="I31:I36" si="7">SUM($D$30:$D$36)</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D32" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="F32" s="3">
         <v>10</v>
       </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="1">
-        <v>5</v>
-      </c>
-      <c r="J32" s="4">
-        <v>1500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H32" s="7">
+        <f t="shared" si="0"/>
+        <v>0.15094339622641509</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="7"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D33" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E33" s="3">
-        <v>5</v>
+        <f t="shared" si="2"/>
+        <v>0.08</v>
       </c>
       <c r="F33" s="3">
-        <v>20</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="1">
-        <v>4</v>
-      </c>
-      <c r="J33" s="4">
-        <v>3150</v>
-      </c>
-      <c r="K33" s="3">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>0.32</v>
+      </c>
+      <c r="H33" s="7">
+        <f t="shared" si="0"/>
+        <v>0.22641509433962265</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="7"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E34" s="3">
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="F34" s="3">
-        <v>40</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="1">
-        <v>3</v>
-      </c>
-      <c r="J34" s="4">
-        <v>6620</v>
-      </c>
-      <c r="K34" s="3">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="H34" s="7">
+        <f t="shared" si="0"/>
+        <v>0.18867924528301888</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="7"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="F35" s="3">
-        <v>80</v>
-      </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="1">
-        <v>2</v>
-      </c>
-      <c r="J35" s="4">
-        <v>13910</v>
-      </c>
-      <c r="K35" s="3">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="H35" s="7">
+        <f t="shared" si="0"/>
+        <v>3.7735849056603772E-2</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="7"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="3">
-        <v>40</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>160</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="1">
-        <v>1</v>
-      </c>
-      <c r="J36" s="4">
-        <v>29220</v>
-      </c>
-      <c r="K36" s="3">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="H36" s="7">
+        <f t="shared" si="0"/>
+        <v>1.8867924528301886E-2</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="7"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E37" s="3">
-        <v>80</v>
+        <f t="shared" si="2"/>
+        <v>128</v>
       </c>
       <c r="F37" s="3">
-        <v>320</v>
-      </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4">
-        <v>61370</v>
-      </c>
-      <c r="K37" s="3">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>512</v>
+      </c>
+      <c r="H37" s="7">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" ref="I37:I42" si="8">SUM($D$37:$D$43)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
       </c>
       <c r="E38" s="3">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>128</v>
       </c>
       <c r="F38" s="3">
-        <v>10</v>
-      </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="4">
-        <v>1500</v>
-      </c>
-      <c r="K38" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>512</v>
+      </c>
+      <c r="H38" s="7">
+        <f t="shared" si="0"/>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="3">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="F39" s="3">
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="1">
-        <v>4</v>
-      </c>
-      <c r="J39" s="4">
-        <v>3150</v>
-      </c>
-      <c r="K39" s="3">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H39" s="7">
+        <f t="shared" si="0"/>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E40" s="3">
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.16</v>
       </c>
       <c r="F40" s="3">
-        <v>40</v>
-      </c>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="1">
-        <v>3</v>
-      </c>
-      <c r="J40" s="4">
-        <v>6620</v>
-      </c>
-      <c r="K40" s="3">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>0.64</v>
+      </c>
+      <c r="H40" s="7">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E41" s="3">
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="F41" s="3">
-        <v>80</v>
-      </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="1">
-        <v>2</v>
-      </c>
-      <c r="J41" s="4">
-        <v>13910</v>
-      </c>
-      <c r="K41" s="3">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="H41" s="7">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="3">
-        <v>40</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="F42" s="3">
-        <v>160</v>
-      </c>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="1">
-        <v>1</v>
-      </c>
-      <c r="J42" s="4">
-        <v>29220</v>
-      </c>
-      <c r="K42" s="3">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="H42" s="7">
+        <f t="shared" si="0"/>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="3">
-        <v>80</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="F43" s="3">
-        <v>320</v>
-      </c>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4">
-        <v>61370</v>
-      </c>
-      <c r="K43" s="3">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="H43" s="7">
+        <f t="shared" si="0"/>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="I43" s="3">
+        <f>SUM($D$37:$D$43)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="4"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="4"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="4"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="4"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="4"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="4"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="4"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="4"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="4"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="4"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="4"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="4"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="4"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="4"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="4"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="4"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="4"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="4"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="5"/>
-      <c r="J78" s="4"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="5"/>
-      <c r="J79" s="4"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="5"/>
-      <c r="J80" s="4"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="5"/>
-      <c r="J81" s="4"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="5"/>
-      <c r="J82" s="4"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="5"/>
-      <c r="J83" s="4"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="4"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="5"/>
-      <c r="J85" s="4"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="5"/>
-      <c r="J86" s="4"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="4"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="4"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="5"/>
-      <c r="J89" s="4"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="4"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="4"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="4"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="4"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="4"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="4"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="4"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="4"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="4"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="4"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="4"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="4"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="4"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="4"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="4"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="4"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="4"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-      <c r="I107" s="5"/>
-      <c r="J107" s="4"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-      <c r="I108" s="5"/>
-      <c r="J108" s="4"/>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="5"/>
-      <c r="J109" s="4"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="5"/>
-      <c r="J110" s="4"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="4"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="4"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="5"/>
-      <c r="J113" s="4"/>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="4"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="5"/>
-      <c r="J115" s="4"/>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="5"/>
-      <c r="J116" s="4"/>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="4"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="5"/>
-      <c r="J118" s="4"/>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="5"/>
-      <c r="J119" s="4"/>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="5"/>
-      <c r="J120" s="4"/>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="5"/>
-      <c r="J121" s="4"/>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
-      <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
-      <c r="I122" s="5"/>
-      <c r="J122" s="4"/>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
-      <c r="I123" s="5"/>
-      <c r="J123" s="4"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
-      <c r="I124" s="5"/>
-      <c r="J124" s="4"/>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
-      <c r="G125" s="3"/>
-      <c r="H125" s="3"/>
-      <c r="I125" s="5"/>
-      <c r="J125" s="4"/>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-      <c r="H126" s="3"/>
-      <c r="I126" s="5"/>
-      <c r="J126" s="4"/>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
-      <c r="I127" s="5"/>
-      <c r="J127" s="4"/>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="3"/>
-      <c r="I128" s="5"/>
-      <c r="J128" s="4"/>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
-      <c r="I129" s="5"/>
-      <c r="J129" s="4"/>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
-      <c r="G130" s="3"/>
-      <c r="H130" s="3"/>
-      <c r="I130" s="5"/>
-      <c r="J130" s="4"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
-      <c r="G131" s="3"/>
-      <c r="H131" s="3"/>
-      <c r="I131" s="5"/>
-      <c r="J131" s="4"/>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
-      <c r="G132" s="3"/>
-      <c r="H132" s="3"/>
-      <c r="I132" s="5"/>
-      <c r="J132" s="4"/>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
-      <c r="G133" s="3"/>
-      <c r="H133" s="3"/>
-      <c r="I133" s="5"/>
-      <c r="J133" s="4"/>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
-      <c r="G134" s="3"/>
-      <c r="H134" s="3"/>
-      <c r="I134" s="5"/>
-      <c r="J134" s="4"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
-      <c r="G135" s="3"/>
-      <c r="H135" s="3"/>
-      <c r="I135" s="5"/>
-      <c r="J135" s="4"/>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
-      <c r="G136" s="3"/>
-      <c r="H136" s="3"/>
-      <c r="I136" s="5"/>
-      <c r="J136" s="4"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
-      <c r="G137" s="3"/>
-      <c r="H137" s="3"/>
-      <c r="I137" s="5"/>
-      <c r="J137" s="4"/>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
-      <c r="G138" s="3"/>
-      <c r="H138" s="3"/>
-      <c r="I138" s="5"/>
-      <c r="J138" s="4"/>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
-      <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
-      <c r="I139" s="5"/>
-      <c r="J139" s="4"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
-      <c r="G140" s="3"/>
-      <c r="H140" s="3"/>
-      <c r="I140" s="5"/>
-      <c r="J140" s="4"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
-      <c r="G141" s="3"/>
-      <c r="H141" s="3"/>
-      <c r="I141" s="5"/>
-      <c r="J141" s="4"/>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
-      <c r="G142" s="3"/>
-      <c r="H142" s="3"/>
-      <c r="I142" s="5"/>
-      <c r="J142" s="4"/>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
-      <c r="G143" s="3"/>
-      <c r="H143" s="3"/>
-      <c r="I143" s="5"/>
-      <c r="J143" s="4"/>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
-      <c r="G144" s="3"/>
-      <c r="H144" s="3"/>
-      <c r="I144" s="5"/>
-      <c r="J144" s="4"/>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
-      <c r="G145" s="3"/>
-      <c r="H145" s="3"/>
-      <c r="I145" s="5"/>
-      <c r="J145" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{14387E03-B723-4008-8D4C-98C0A6225079}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B43" xr:uid="{6F7C22CB-3302-4FCE-BE29-634B012439FF}">
-      <formula1>$P$2:$P$7</formula1>
+      <formula1>$L$2:$L$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C43" xr:uid="{061ACE8B-28B7-46EA-8228-C23E0DB18982}">
-      <formula1>$O$2:$O$8</formula1>
+      <formula1>$K$2:$K$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{14387E03-B723-4008-8D4C-98C0A6225079}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H1:H1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/Assets/AddressableResource/Data/Excels/TowerWeaponJewelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/TowerWeaponJewelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21E10A6-5F50-4DEB-A5E8-1360F392A909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC14FB6-F491-4C60-BA7D-15433FD4B367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -32,8 +32,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="43">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -151,6 +173,44 @@
   </si>
   <si>
     <t>grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkMul</t>
+  </si>
+  <si>
+    <t>AtkMul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CriDmgMul</t>
+  </si>
+  <si>
+    <t>CriDmgMul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -238,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -261,11 +321,20 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -566,17 +635,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:Q155"/>
   <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="18.875" style="5" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="6" customWidth="1"/>
     <col min="6" max="6" width="19" style="6" customWidth="1"/>
-    <col min="7" max="12" width="17.625" style="3"/>
-    <col min="14" max="16384" width="17.625" style="3"/>
+    <col min="7" max="10" width="17.625" style="3"/>
+    <col min="11" max="12" width="10.625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.625" customWidth="1"/>
+    <col min="14" max="16" width="10.625" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="17.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
@@ -602,7 +674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -613,7 +685,7 @@
         <v>21</v>
       </c>
       <c r="D2" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3">
         <v>0</v>
@@ -622,12 +694,12 @@
         <v>16</v>
       </c>
       <c r="H2" s="7">
-        <f t="shared" ref="H2:H43" si="0">D2/I2</f>
-        <v>0.16666666666666666</v>
+        <f t="shared" ref="H2:H55" si="0">D2/I2</f>
+        <v>6.5217391304347824E-2</v>
       </c>
       <c r="I2" s="3">
-        <f>SUM($D$2:$D$8)</f>
-        <v>6</v>
+        <f>SUM($D$2:$D$10)</f>
+        <v>46</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>22</v>
@@ -636,7 +708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -647,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -657,11 +729,11 @@
       </c>
       <c r="H3" s="7">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I8" si="1">SUM($D$2:$D$8)</f>
-        <v>6</v>
+        <f t="shared" ref="I3:I10" si="1">SUM($D$2:$D$10)</f>
+        <v>46</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>24</v>
@@ -670,7 +742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -681,7 +753,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -691,11 +763,11 @@
       </c>
       <c r="H4" s="7">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>26</v>
@@ -704,7 +776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -715,7 +787,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -725,11 +797,11 @@
       </c>
       <c r="H5" s="7">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>6.5217391304347824E-2</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>28</v>
@@ -738,7 +810,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -763,7 +835,7 @@
       </c>
       <c r="I6" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>30</v>
@@ -772,7 +844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -797,7 +869,7 @@
       </c>
       <c r="I7" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -806,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -831,112 +903,105 @@
       </c>
       <c r="I8" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" ref="H9:H10" si="2">D9/I9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D11" s="1">
         <v>5</v>
       </c>
-      <c r="E9" s="3">
-        <f>F2/2</f>
+      <c r="E11" s="3">
+        <f t="shared" ref="E11:E17" si="3">F2/2</f>
         <v>8</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F11" s="3">
         <f>F2*2</f>
         <v>32</v>
       </c>
-      <c r="H9" s="7">
-        <f t="shared" si="0"/>
-        <v>0.17241379310344829</v>
-      </c>
-      <c r="I9" s="3">
-        <f>SUM($D$9:$D$15)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="1">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3">
-        <f t="shared" ref="E10:E43" si="2">F3/2</f>
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <f t="shared" ref="F10:F43" si="3">F3*2</f>
-        <v>32</v>
-      </c>
-      <c r="H10" s="7">
-        <f t="shared" si="0"/>
-        <v>0.31034482758620691</v>
-      </c>
-      <c r="I10" s="3">
-        <f t="shared" ref="I10:I15" si="4">SUM($D$9:$D$15)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="1">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
       <c r="H11" s="7">
         <f t="shared" si="0"/>
-        <v>0.31034482758620691</v>
+        <v>9.8039215686274508E-2</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="4"/>
-        <v>29</v>
-      </c>
-      <c r="J11" s="1">
-        <v>5</v>
-      </c>
-      <c r="K11" s="4">
-        <v>1500</v>
-      </c>
-      <c r="L11" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <f>SUM($D$11:$D$19)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -944,115 +1009,117 @@
         <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="1">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
+        <f>F3*2</f>
+        <v>32</v>
+      </c>
+      <c r="H12" s="7">
+        <f t="shared" si="0"/>
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" ref="I12:I19" si="4">SUM($D$11:$D$19)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="1">
+        <v>20</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <f>F4*2</f>
+        <v>4</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="0"/>
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="4"/>
+        <v>51</v>
+      </c>
+      <c r="J13" s="1">
+        <v>3</v>
+      </c>
+      <c r="K13" s="4">
+        <v>1500</v>
+      </c>
+      <c r="L13" s="3">
+        <f>K13*2</f>
+        <v>3000</v>
+      </c>
+      <c r="M13">
+        <f>K13/(J13/100)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D14" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="3">
-        <f t="shared" si="2"/>
+      <c r="E14" s="3">
+        <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F14" s="3">
         <f>F5*2</f>
         <v>0.04</v>
       </c>
-      <c r="H12" s="7">
-        <f t="shared" si="0"/>
-        <v>0.17241379310344829</v>
-      </c>
-      <c r="I12" s="3">
-        <f t="shared" si="4"/>
-        <v>29</v>
-      </c>
-      <c r="J12" s="1">
-        <v>4</v>
-      </c>
-      <c r="K12" s="4">
-        <v>3150</v>
-      </c>
-      <c r="L12" s="3">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>2</v>
-      </c>
-      <c r="H13" s="7">
-        <f t="shared" si="0"/>
-        <v>3.4482758620689655E-2</v>
-      </c>
-      <c r="I13" s="3">
-        <f t="shared" si="4"/>
-        <v>29</v>
-      </c>
-      <c r="J13" s="1">
-        <v>3</v>
-      </c>
-      <c r="K13" s="4">
-        <v>6620</v>
-      </c>
-      <c r="L13" s="3">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="H14" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.8039215686274508E-2</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="J14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="4">
-        <v>13910</v>
+        <v>3150</v>
       </c>
       <c r="L14" s="3">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <f t="shared" ref="L14" si="5">K14*2</f>
+        <v>6300</v>
+      </c>
+      <c r="M14">
+        <f t="shared" ref="M14:M17" si="6">K14/(J14/100)</f>
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1060,178 +1127,198 @@
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.9607843137254902E-2</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="J15" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K15" s="4">
-        <v>29220</v>
+        <v>6620</v>
       </c>
       <c r="L15" s="3">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <f>K15*3</f>
+        <v>19860</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="6"/>
+        <v>827500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="2"/>
-        <v>16</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="3"/>
-        <v>64</v>
+        <f>F7*2</f>
+        <v>0</v>
       </c>
       <c r="H16" s="7">
         <f t="shared" si="0"/>
-        <v>0.18181818181818182</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3">
-        <f>SUM($D$16:$D$22)</f>
-        <v>11</v>
+        <f t="shared" si="4"/>
+        <v>51</v>
       </c>
       <c r="J16" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K16" s="4">
-        <v>61370</v>
+        <v>13910</v>
       </c>
       <c r="L16" s="3">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <f>K16*3</f>
+        <v>41730</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="6"/>
+        <v>2782000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="2"/>
-        <v>16</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="3"/>
-        <v>64</v>
+        <f>F8*2</f>
+        <v>0</v>
       </c>
       <c r="H17" s="7">
         <f t="shared" si="0"/>
-        <v>0.27272727272727271</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" ref="I17:I22" si="5">SUM($D$16:$D$22)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>51</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="K17" s="4">
+        <v>29220</v>
+      </c>
+      <c r="L17" s="3">
+        <f>K17*4</f>
+        <v>116880</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="6"/>
+        <v>9740000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7">
         <f t="shared" si="0"/>
-        <v>0.27272727272727271</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>51</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>61370</v>
+      </c>
+      <c r="L18" s="3">
+        <f>K18*4</f>
+        <v>245480</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="2"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="3"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="0"/>
-        <v>0.18181818181818182</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="J19" s="3">
-        <v>5</v>
-      </c>
-      <c r="K19" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="4"/>
+        <v>51</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1239,34 +1326,29 @@
         <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" ref="E20:E26" si="7">F11/2</f>
+        <v>16</v>
       </c>
       <c r="F20" s="3">
-        <v>4</v>
+        <f>F11*2</f>
+        <v>64</v>
       </c>
       <c r="H20" s="7">
         <f t="shared" si="0"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.12244897959183673</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="J20" s="3">
-        <v>10</v>
-      </c>
-      <c r="K20" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <f>SUM($D$20:$D$28)</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1274,35 +1356,30 @@
         <v>8</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>16</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>F12*2</f>
+        <v>64</v>
       </c>
       <c r="H21" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.34693877551020408</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="J21" s="3">
-        <v>20</v>
-      </c>
-      <c r="K21" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" ref="I21:I28" si="8">SUM($D$20:$D$28)</f>
+        <v>49</v>
+      </c>
+      <c r="J21" s="7"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1310,218 +1387,332 @@
         <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.34693877551020408</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="J22" s="3">
-        <v>40</v>
-      </c>
-      <c r="K22" s="3">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D23" s="1">
         <v>6</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="2"/>
-        <v>32</v>
+        <f t="shared" si="7"/>
+        <v>0.02</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="3"/>
-        <v>128</v>
+        <f>F14*2</f>
+        <v>0.08</v>
       </c>
       <c r="H23" s="7">
         <f t="shared" si="0"/>
-        <v>0.20689655172413793</v>
+        <v>0.12244897959183673</v>
       </c>
       <c r="I23" s="3">
-        <f>SUM($D$23:$D$29)</f>
-        <v>29</v>
-      </c>
-      <c r="J23" s="3">
-        <v>80</v>
-      </c>
-      <c r="K23" s="3">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D24" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="2"/>
-        <v>32</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="3"/>
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="H24" s="7">
         <f t="shared" si="0"/>
-        <v>0.20689655172413793</v>
+        <v>4.0816326530612242E-2</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" ref="I24:I29" si="6">SUM($D$23:$D$29)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D25" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H25" s="7">
         <f t="shared" si="0"/>
-        <v>0.20689655172413793</v>
+        <v>2.0408163265306121E-2</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="6"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="7" cm="1">
+        <f t="array" ref="K25">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>6.5217391304347824E-2</v>
+      </c>
+      <c r="L25" s="7" cm="1">
+        <f t="array" ref="L25">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>9.8039215686274508E-2</v>
+      </c>
+      <c r="M25" s="7" cm="1">
+        <f t="array" ref="M25">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="N25" s="7" cm="1">
+        <f t="array" ref="N25">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.1875</v>
+      </c>
+      <c r="O25" s="7" cm="1">
+        <f t="array" ref="O25">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.20338983050847459</v>
+      </c>
+      <c r="P25" s="7" cm="1">
+        <f t="array" ref="P25">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="Q25" s="7"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D26" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="2"/>
-        <v>0.04</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="3"/>
-        <v>0.16</v>
+        <f>F17*2</f>
+        <v>0</v>
       </c>
       <c r="H26" s="7">
         <f t="shared" si="0"/>
-        <v>0.20689655172413793</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="6"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="7" cm="1">
+        <f t="array" ref="K26">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.43478260869565216</v>
+      </c>
+      <c r="L26" s="7" cm="1">
+        <f t="array" ref="L26">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="M26" s="7" cm="1">
+        <f t="array" ref="M26">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.34693877551020408</v>
+      </c>
+      <c r="N26" s="7" cm="1">
+        <f t="array" ref="N26">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.25</v>
+      </c>
+      <c r="O26" s="7" cm="1">
+        <f t="array" ref="O26">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.20338983050847459</v>
+      </c>
+      <c r="P26" s="7" cm="1">
+        <f t="array" ref="P26">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.19298245614035087</v>
+      </c>
+      <c r="Q26" s="7"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7">
         <f t="shared" si="0"/>
-        <v>0.13793103448275862</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="6"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="7" cm="1">
+        <f t="array" ref="K27">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.43478260869565216</v>
+      </c>
+      <c r="L27" s="7" cm="1">
+        <f t="array" ref="L27">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="M27" s="7" cm="1">
+        <f t="array" ref="M27">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.34693877551020408</v>
+      </c>
+      <c r="N27" s="7" cm="1">
+        <f t="array" ref="N27">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.25</v>
+      </c>
+      <c r="O27" s="7" cm="1">
+        <f t="array" ref="O27">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.20338983050847459</v>
+      </c>
+      <c r="P27" s="7" cm="1">
+        <f t="array" ref="P27">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.19298245614035087</v>
+      </c>
+      <c r="Q27" s="7"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F28" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="7">
         <f t="shared" si="0"/>
-        <v>3.4482758620689655E-2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" si="6"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>49</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28" s="7" cm="1">
+        <f t="array" ref="K28">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>6.5217391304347824E-2</v>
+      </c>
+      <c r="L28" s="7" cm="1">
+        <f t="array" ref="L28">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>9.8039215686274508E-2</v>
+      </c>
+      <c r="M28" s="7" cm="1">
+        <f t="array" ref="M28">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="N28" s="7" cm="1">
+        <f t="array" ref="N28">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.1875</v>
+      </c>
+      <c r="O28" s="7" cm="1">
+        <f t="array" ref="O28">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.20338983050847459</v>
+      </c>
+      <c r="P28" s="7" cm="1">
+        <f t="array" ref="P28">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="Q28" s="7"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1529,540 +1720,930 @@
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" ref="E29:E35" si="9">F20/2</f>
+        <v>32</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>F20*2</f>
+        <v>128</v>
       </c>
       <c r="H29" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="6"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <f>SUM($D$29:$D$37)</f>
+        <v>48</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="7" cm="1">
+        <f t="array" ref="K29">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7" cm="1">
+        <f t="array" ref="L29">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>1.9607843137254902E-2</v>
+      </c>
+      <c r="M29" s="7" cm="1">
+        <f t="array" ref="M29">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>4.0816326530612242E-2</v>
+      </c>
+      <c r="N29" s="7" cm="1">
+        <f t="array" ref="N29">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="O29" s="7" cm="1">
+        <f t="array" ref="O29">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>6.7796610169491525E-2</v>
+      </c>
+      <c r="P29" s="7" cm="1">
+        <f t="array" ref="P29">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>7.0175438596491224E-2</v>
+      </c>
+      <c r="Q29" s="7"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D30" s="1">
         <v>12</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="2"/>
-        <v>64</v>
+        <f t="shared" si="9"/>
+        <v>32</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="3"/>
-        <v>256</v>
+        <f>F21*2</f>
+        <v>128</v>
       </c>
       <c r="H30" s="7">
         <f t="shared" si="0"/>
-        <v>0.22641509433962265</v>
+        <v>0.25</v>
       </c>
       <c r="I30" s="3">
-        <f>SUM($D$30:$D$36)</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" ref="I30:I37" si="10">SUM($D$29:$D$37)</f>
+        <v>48</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="7" cm="1">
+        <f t="array" ref="K30">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="7" cm="1">
+        <f t="array" ref="L30">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="7" cm="1">
+        <f t="array" ref="M30">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="N30" s="7" cm="1">
+        <f t="array" ref="N30">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="O30" s="7" cm="1">
+        <f t="array" ref="O30">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="P30" s="7" cm="1">
+        <f t="array" ref="P30">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Q30" s="7"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="1">
         <v>12</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="E31" s="3">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="F31" s="3">
         <v>8</v>
       </c>
-      <c r="E31" s="3">
-        <f t="shared" si="2"/>
-        <v>64</v>
-      </c>
-      <c r="F31" s="3">
-        <f t="shared" si="3"/>
-        <v>256</v>
-      </c>
       <c r="H31" s="7">
         <f t="shared" si="0"/>
-        <v>0.15094339622641509</v>
+        <v>0.25</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" ref="I31:I36" si="7">SUM($D$30:$D$36)</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="7" cm="1">
+        <f t="array" ref="K31">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="7" cm="1">
+        <f t="array" ref="L31">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="7" cm="1">
+        <f t="array" ref="M31">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="7" cm="1">
+        <f t="array" ref="N31">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="O31" s="7" cm="1">
+        <f t="array" ref="O31">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>3.3898305084745763E-2</v>
+      </c>
+      <c r="P31" s="7" cm="1">
+        <f t="array" ref="P31">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>3.5087719298245612E-2</v>
+      </c>
+      <c r="Q31" s="7"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>0.04</v>
       </c>
       <c r="F32" s="3">
-        <v>10</v>
+        <f>F23*2</f>
+        <v>0.16</v>
       </c>
       <c r="H32" s="7">
         <f t="shared" si="0"/>
-        <v>0.15094339622641509</v>
+        <v>0.1875</v>
       </c>
       <c r="I32" s="3">
-        <f t="shared" si="7"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="7" cm="1">
+        <f t="array" ref="K32">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="7" cm="1">
+        <f t="array" ref="L32">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" cm="1">
+        <f t="array" ref="M32">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="7" cm="1">
+        <f t="array" ref="N32">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="O32" s="7" cm="1">
+        <f t="array" ref="O32">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="P32" s="7" cm="1">
+        <f t="array" ref="P32">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>1.7543859649122806E-2</v>
+      </c>
+      <c r="Q32" s="7"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D33" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="2"/>
-        <v>0.08</v>
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="3"/>
-        <v>0.32</v>
+        <v>6</v>
       </c>
       <c r="H33" s="7">
         <f t="shared" si="0"/>
-        <v>0.22641509433962265</v>
+        <v>6.25E-2</v>
       </c>
       <c r="I33" s="3">
-        <f t="shared" si="7"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33" s="7" cm="1">
+        <f t="array" ref="K33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="7" cm="1">
+        <f t="array" ref="L33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="7" cm="1">
+        <f t="array" ref="M33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="7" cm="1">
+        <f t="array" ref="N33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="7" cm="1">
+        <f t="array" ref="O33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="P33" s="7" cm="1">
+        <f t="array" ref="P33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
+        <v>1.7543859649122806E-2</v>
+      </c>
+      <c r="Q33" s="7"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D34" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" si="9"/>
+        <v>1</v>
       </c>
       <c r="F34" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H34" s="7">
         <f t="shared" si="0"/>
-        <v>0.18867924528301888</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="I34" s="3">
-        <f t="shared" si="7"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>2</v>
       </c>
-      <c r="E35" s="3">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="F35" s="3">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
       <c r="H35" s="7">
         <f t="shared" si="0"/>
-        <v>3.7735849056603772E-2</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" si="7"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H36" s="7">
         <f t="shared" si="0"/>
-        <v>1.8867924528301886E-2</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3">
-        <f t="shared" si="7"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D37" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E37" s="3">
-        <f t="shared" si="2"/>
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3">
-        <f t="shared" si="3"/>
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I37" s="3">
-        <f t="shared" ref="I37:I42" si="8">SUM($D$37:$D$43)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D38" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" si="2"/>
-        <v>128</v>
+        <f t="shared" ref="E38:E43" si="11">F29/2</f>
+        <v>64</v>
       </c>
       <c r="F38" s="3">
-        <f t="shared" si="3"/>
-        <v>512</v>
+        <f>F29*2</f>
+        <v>256</v>
       </c>
       <c r="H38" s="7">
         <f t="shared" si="0"/>
-        <v>0.10714285714285714</v>
+        <v>0.20338983050847459</v>
       </c>
       <c r="I38" s="3">
-        <f t="shared" si="8"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <f>SUM($D$38:$D$46)</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D39" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E39" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="11"/>
+        <v>64</v>
       </c>
       <c r="F39" s="3">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <f>F30*2</f>
+        <v>256</v>
       </c>
       <c r="H39" s="7">
         <f t="shared" si="0"/>
-        <v>3.5714285714285712E-2</v>
+        <v>0.20338983050847459</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" si="8"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" ref="I39:I46" si="12">SUM($D$38:$D$46)</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D40" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E40" s="3">
-        <f t="shared" si="2"/>
-        <v>0.16</v>
+        <f t="shared" si="11"/>
+        <v>4</v>
       </c>
       <c r="F40" s="3">
-        <f t="shared" si="3"/>
-        <v>0.64</v>
+        <v>10</v>
       </c>
       <c r="H40" s="7">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0.20338983050847459</v>
       </c>
       <c r="I40" s="3">
-        <f t="shared" si="8"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D41" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E41" s="3">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f t="shared" si="11"/>
+        <v>0.08</v>
       </c>
       <c r="F41" s="3">
-        <v>12</v>
+        <v>0.2</v>
       </c>
       <c r="H41" s="7">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0.20338983050847459</v>
       </c>
       <c r="I41" s="3">
-        <f t="shared" si="8"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D42" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f t="shared" si="11"/>
+        <v>3</v>
       </c>
       <c r="F42" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H42" s="7">
         <f t="shared" si="0"/>
-        <v>7.1428571428571425E-2</v>
+        <v>6.7796610169491525E-2</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" si="8"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="F43" s="3">
+        <f>F34*2</f>
+        <v>8</v>
+      </c>
+      <c r="H43" s="7">
+        <f t="shared" si="0"/>
+        <v>5.0847457627118647E-2</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1</v>
+      </c>
+      <c r="F44" s="3">
+        <v>6</v>
+      </c>
+      <c r="H44" s="7">
+        <f t="shared" si="0"/>
+        <v>3.3898305084745763E-2</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4</v>
+      </c>
+      <c r="H45" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="I45" s="3">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>4</v>
+      </c>
+      <c r="H46" s="7">
+        <f t="shared" si="0"/>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="12"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="1">
+        <v>12</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" ref="E47:E53" si="13">F38/2</f>
+        <v>128</v>
+      </c>
+      <c r="F47" s="3">
+        <v>400</v>
+      </c>
+      <c r="H47" s="7">
+        <f t="shared" si="0"/>
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="I47" s="3">
+        <f>SUM($D$47:$D$55)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="1">
+        <v>11</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="13"/>
+        <v>128</v>
+      </c>
+      <c r="F48" s="3">
+        <v>400</v>
+      </c>
+      <c r="H48" s="7">
+        <f t="shared" si="0"/>
+        <v>0.19298245614035087</v>
+      </c>
+      <c r="I48" s="3">
+        <f t="shared" ref="I48:I55" si="14">SUM($D$47:$D$55)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="1">
+        <v>11</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="F49" s="3">
+        <f t="shared" ref="F49:F50" si="15">F40*2</f>
+        <v>20</v>
+      </c>
+      <c r="H49" s="7">
+        <f t="shared" si="0"/>
+        <v>0.19298245614035087</v>
+      </c>
+      <c r="I49" s="3">
+        <f t="shared" si="14"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="1">
+        <v>12</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" si="13"/>
+        <v>0.1</v>
+      </c>
+      <c r="F50" s="3">
+        <f t="shared" si="15"/>
+        <v>0.4</v>
+      </c>
+      <c r="H50" s="7">
+        <f t="shared" si="0"/>
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="14"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="F51" s="3">
+        <v>10</v>
+      </c>
+      <c r="H51" s="7">
+        <f t="shared" si="0"/>
+        <v>7.0175438596491224E-2</v>
+      </c>
+      <c r="I51" s="3">
+        <f t="shared" si="14"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="1">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="F52" s="3">
+        <v>10</v>
+      </c>
+      <c r="H52" s="7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="14"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="F53" s="3">
+        <v>10</v>
+      </c>
+      <c r="H53" s="7">
+        <f t="shared" si="0"/>
+        <v>3.5087719298245612E-2</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="14"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="1">
         <v>1</v>
       </c>
-      <c r="E43" s="3">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="F43" s="3">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="H43" s="7">
-        <f t="shared" si="0"/>
-        <v>3.5714285714285712E-2</v>
-      </c>
-      <c r="I43" s="3">
-        <f>SUM($D$37:$D$43)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E54" s="3">
+        <v>1</v>
+      </c>
+      <c r="F54" s="3">
+        <v>8</v>
+      </c>
+      <c r="H54" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7543859649122806E-2</v>
+      </c>
+      <c r="I54" s="3">
+        <f t="shared" si="14"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3">
+        <v>1</v>
+      </c>
+      <c r="F55" s="3">
+        <v>8</v>
+      </c>
+      <c r="H55" s="7">
+        <f t="shared" si="0"/>
+        <v>1.7543859649122806E-2</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="14"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2070,7 +2651,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2078,7 +2659,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2086,7 +2667,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2094,7 +2675,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2102,7 +2683,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2110,7 +2691,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2118,7 +2699,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2126,7 +2707,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2782,10 +3363,90 @@
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
     </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2798,12 +3459,29 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K25:P33">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>K25&lt;J25</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F5EABCE3-5819-489A-B937-36AA7AA5338B}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B43" xr:uid="{6F7C22CB-3302-4FCE-BE29-634B012439FF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B55" xr:uid="{6F7C22CB-3302-4FCE-BE29-634B012439FF}">
       <formula1>$L$2:$L$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C43" xr:uid="{061ACE8B-28B7-46EA-8228-C23E0DB18982}">
-      <formula1>$K$2:$K$8</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C55" xr:uid="{061ACE8B-28B7-46EA-8228-C23E0DB18982}">
+      <formula1>$K$2:$K$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2824,6 +3502,19 @@
           </x14:cfRule>
           <xm:sqref>H1:H1048576</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F5EABCE3-5819-489A-B937-36AA7AA5338B}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K25:P33</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/Assets/AddressableResource/Data/Excels/TowerWeaponJewelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/TowerWeaponJewelData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC14FB6-F491-4C60-BA7D-15433FD4B367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D799CC7-582B-493C-91FD-9B4BEEF6BB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="41">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,13 +180,6 @@
   </si>
   <si>
     <t>AtkMul</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CriDmgMul</t>
-  </si>
-  <si>
-    <t>CriDmgMul</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -698,7 +691,7 @@
         <v>6.5217391304347824E-2</v>
       </c>
       <c r="I2" s="3">
-        <f>SUM($D$2:$D$10)</f>
+        <f t="shared" ref="I2:I8" si="1">SUM($D$2:$D$9)</f>
         <v>46</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -732,7 +725,7 @@
         <v>0.43478260869565216</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I10" si="1">SUM($D$2:$D$10)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="K3" s="3" t="s">
@@ -933,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" si="1"/>
+        <f>SUM($D$2:$D$9)</f>
         <v>46</v>
       </c>
       <c r="K9" s="3" t="s">
@@ -945,31 +938,23 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <f>F2/2</f>
+        <v>8</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>36</v>
-      </c>
+        <f>F2*2</f>
+        <v>32</v>
+      </c>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
@@ -979,25 +964,25 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E11" s="3">
-        <f t="shared" ref="E11:E17" si="3">F2/2</f>
+        <f>F3/2</f>
         <v>8</v>
       </c>
       <c r="F11" s="3">
-        <f>F2*2</f>
+        <f>F3*2</f>
         <v>32</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="0"/>
+        <f>D10/I11</f>
         <v>9.8039215686274508E-2</v>
       </c>
       <c r="I11" s="3">
-        <f>SUM($D$11:$D$19)</f>
+        <f>SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
     </row>
@@ -1009,25 +994,25 @@
         <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1">
         <v>20</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="3"/>
-        <v>8</v>
+        <f>F4/2</f>
+        <v>1</v>
       </c>
       <c r="F12" s="3">
-        <f>F3*2</f>
-        <v>32</v>
+        <f>F4*2</f>
+        <v>4</v>
       </c>
       <c r="H12" s="7">
-        <f t="shared" si="0"/>
+        <f>D11/I12</f>
         <v>0.39215686274509803</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" ref="I12:I19" si="4">SUM($D$11:$D$19)</f>
+        <f>SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
     </row>
@@ -1039,25 +1024,25 @@
         <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E13" s="3">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f>F5/2</f>
+        <v>0.01</v>
       </c>
       <c r="F13" s="3">
-        <f>F4*2</f>
-        <v>4</v>
+        <f>F5*2</f>
+        <v>0.04</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" si="0"/>
+        <f>D12/I13</f>
         <v>0.39215686274509803</v>
       </c>
       <c r="I13" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
       <c r="J13" s="1">
@@ -1083,25 +1068,24 @@
         <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" si="3"/>
-        <v>0.01</v>
+        <f>F6/2</f>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <f>F5*2</f>
-        <v>0.04</v>
+        <v>2</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="0"/>
+        <f>D13/I14</f>
         <v>9.8039215686274508E-2</v>
       </c>
       <c r="I14" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
       <c r="J14" s="1">
@@ -1111,11 +1095,11 @@
         <v>3150</v>
       </c>
       <c r="L14" s="3">
-        <f t="shared" ref="L14" si="5">K14*2</f>
+        <f t="shared" ref="L14" si="3">K14*2</f>
         <v>6300</v>
       </c>
       <c r="M14">
-        <f t="shared" ref="M14:M17" si="6">K14/(J14/100)</f>
+        <f t="shared" ref="M14:M17" si="4">K14/(J14/100)</f>
         <v>315000</v>
       </c>
     </row>
@@ -1127,24 +1111,25 @@
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="3"/>
+        <f>F7/2</f>
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>2</v>
+        <f>F7*2</f>
+        <v>0</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="0"/>
+        <f>D14/I15</f>
         <v>1.9607843137254902E-2</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
       <c r="J15" s="1">
@@ -1158,7 +1143,7 @@
         <v>19860</v>
       </c>
       <c r="M15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>827500</v>
       </c>
     </row>
@@ -1170,25 +1155,25 @@
         <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="3"/>
+        <f>F8/2</f>
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f>F7*2</f>
+        <f>F8*2</f>
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="0"/>
+        <f>D15/I16</f>
         <v>0</v>
       </c>
       <c r="I16" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
       <c r="J16" s="1">
@@ -1202,7 +1187,7 @@
         <v>41730</v>
       </c>
       <c r="M16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2782000</v>
       </c>
     </row>
@@ -1214,25 +1199,23 @@
         <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <f>F8*2</f>
         <v>0</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="0"/>
+        <f>D16/I17</f>
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
       <c r="J17" s="1">
@@ -1246,7 +1229,7 @@
         <v>116880</v>
       </c>
       <c r="M17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>9740000</v>
       </c>
     </row>
@@ -1255,26 +1238,28 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="1">
         <v>6</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <f>F10/2</f>
+        <v>16</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <f>F10*2</f>
+        <v>64</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="0"/>
+        <f>D17/I18</f>
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="4"/>
+        <f>SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
       <c r="J18" s="1">
@@ -1293,28 +1278,23 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E19" s="3">
-        <v>0</v>
+        <f>F11/2</f>
+        <v>16</v>
       </c>
       <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <f t="shared" si="4"/>
-        <v>51</v>
-      </c>
+        <f>F11*2</f>
+        <v>64</v>
+      </c>
+      <c r="H19" s="7"/>
       <c r="J19" s="1"/>
       <c r="K19" s="4"/>
     </row>
@@ -1326,25 +1306,24 @@
         <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D20" s="1">
+        <v>17</v>
+      </c>
+      <c r="E20" s="3">
+        <f>F12/2</f>
+        <v>2</v>
+      </c>
+      <c r="F20" s="3">
         <v>6</v>
       </c>
-      <c r="E20" s="3">
-        <f t="shared" ref="E20:E26" si="7">F11/2</f>
-        <v>16</v>
-      </c>
-      <c r="F20" s="3">
-        <f>F11*2</f>
-        <v>64</v>
-      </c>
       <c r="H20" s="7">
-        <f t="shared" si="0"/>
+        <f>D18/I20</f>
         <v>0.12244897959183673</v>
       </c>
       <c r="I20" s="3">
-        <f>SUM($D$20:$D$28)</f>
+        <f>SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
     </row>
@@ -1356,25 +1335,25 @@
         <v>8</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D21" s="1">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E21" s="3">
-        <f t="shared" si="7"/>
-        <v>16</v>
+        <f>F13/2</f>
+        <v>0.02</v>
       </c>
       <c r="F21" s="3">
-        <f>F12*2</f>
-        <v>64</v>
+        <f>F13*2</f>
+        <v>0.08</v>
       </c>
       <c r="H21" s="7">
-        <f t="shared" si="0"/>
+        <f>D19/I21</f>
         <v>0.34693877551020408</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" ref="I21:I28" si="8">SUM($D$20:$D$28)</f>
+        <f>SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
       <c r="J21" s="7"/>
@@ -1387,24 +1366,24 @@
         <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3">
-        <f t="shared" si="7"/>
-        <v>2</v>
+        <f>F14/2</f>
+        <v>1</v>
       </c>
       <c r="F22" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="0"/>
+        <f>D20/I22</f>
         <v>0.34693877551020408</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="8"/>
+        <f>SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
     </row>
@@ -1416,25 +1395,24 @@
         <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E23" s="3">
-        <f t="shared" si="7"/>
-        <v>0.02</v>
+        <f>F15/2</f>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
-        <f>F14*2</f>
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="H23" s="7">
-        <f t="shared" si="0"/>
+        <f>D21/I23</f>
         <v>0.12244897959183673</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="8"/>
+        <f>SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
     </row>
@@ -1446,43 +1424,44 @@
         <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="7"/>
-        <v>1</v>
+        <f>F16/2</f>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>4</v>
+        <f>F16*2</f>
+        <v>0</v>
       </c>
       <c r="H24" s="7">
-        <f t="shared" si="0"/>
+        <f>D22/I24</f>
         <v>4.0816326530612242E-2</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="8"/>
+        <f>SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
       <c r="K24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M24" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="N24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="O24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="P24" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
@@ -1493,24 +1472,23 @@
         <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" si="0"/>
+        <f>D23/I25</f>
         <v>2.0408163265306121E-2</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="8"/>
+        <f>SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
       <c r="J25" s="3" t="s">
@@ -1534,11 +1512,11 @@
       </c>
       <c r="O25" s="7" cm="1">
         <f t="array" ref="O25">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0.20338983050847459</v>
+        <v>0.20689655172413793</v>
       </c>
       <c r="P25" s="7" cm="1">
         <f t="array" ref="P25">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0.21052631578947367</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="Q25" s="7"/>
     </row>
@@ -1547,28 +1525,28 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f>F18/2</f>
+        <v>32</v>
       </c>
       <c r="F26" s="3">
-        <f>F17*2</f>
-        <v>0</v>
+        <f>F18*2</f>
+        <v>128</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="0"/>
+        <f>D24/I26</f>
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="8"/>
+        <f>SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
       <c r="J26" s="3" t="s">
@@ -1592,11 +1570,11 @@
       </c>
       <c r="O26" s="7" cm="1">
         <f t="array" ref="O26">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0.20338983050847459</v>
+        <v>0.20689655172413793</v>
       </c>
       <c r="P26" s="7" cm="1">
         <f t="array" ref="P26">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0.19298245614035087</v>
+        <v>0.19642857142857142</v>
       </c>
       <c r="Q26" s="7"/>
     </row>
@@ -1605,26 +1583,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <f>F19/2</f>
+        <v>32</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <f>F19*2</f>
+        <v>128</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="0"/>
+        <f>D25/I27</f>
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="8"/>
+        <f>SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -1648,11 +1628,11 @@
       </c>
       <c r="O27" s="7" cm="1">
         <f t="array" ref="O27">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0.20338983050847459</v>
+        <v>0.20689655172413793</v>
       </c>
       <c r="P27" s="7" cm="1">
         <f t="array" ref="P27">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0.19298245614035087</v>
+        <v>0.19642857142857142</v>
       </c>
       <c r="Q27" s="7"/>
     </row>
@@ -1661,28 +1641,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="1">
+        <v>12</v>
+      </c>
+      <c r="E28" s="3">
+        <f>F20/2</f>
+        <v>3</v>
+      </c>
+      <c r="F28" s="3">
         <v>8</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="H28" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <f t="shared" si="8"/>
-        <v>49</v>
-      </c>
+      <c r="H28" s="7"/>
       <c r="J28" s="3" t="s">
         <v>28</v>
       </c>
@@ -1704,11 +1678,11 @@
       </c>
       <c r="O28" s="7" cm="1">
         <f t="array" ref="O28">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0.20338983050847459</v>
+        <v>0.20689655172413793</v>
       </c>
       <c r="P28" s="7" cm="1">
         <f t="array" ref="P28">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0.21052631578947367</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="Q28" s="7"/>
     </row>
@@ -1720,25 +1694,25 @@
         <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D29" s="1">
         <v>9</v>
       </c>
       <c r="E29" s="3">
-        <f t="shared" ref="E29:E35" si="9">F20/2</f>
-        <v>32</v>
+        <f>F21/2</f>
+        <v>0.04</v>
       </c>
       <c r="F29" s="3">
-        <f>F20*2</f>
-        <v>128</v>
+        <f>F21*2</f>
+        <v>0.16</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="0"/>
+        <f>D26/I29</f>
         <v>0.1875</v>
       </c>
       <c r="I29" s="3">
-        <f>SUM($D$29:$D$37)</f>
+        <f>SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -1762,11 +1736,11 @@
       </c>
       <c r="O29" s="7" cm="1">
         <f t="array" ref="O29">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>6.7796610169491525E-2</v>
+        <v>6.8965517241379309E-2</v>
       </c>
       <c r="P29" s="7" cm="1">
         <f t="array" ref="P29">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>7.0175438596491224E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="Q29" s="7"/>
     </row>
@@ -1778,25 +1752,24 @@
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D30" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="9"/>
-        <v>32</v>
+        <f>F22/2</f>
+        <v>2</v>
       </c>
       <c r="F30" s="3">
-        <f>F21*2</f>
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="H30" s="7">
-        <f t="shared" si="0"/>
+        <f>D27/I30</f>
         <v>0.25</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" ref="I30:I37" si="10">SUM($D$29:$D$37)</f>
+        <f>SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -1820,11 +1793,11 @@
       </c>
       <c r="O30" s="7" cm="1">
         <f t="array" ref="O30">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>5.0847457627118647E-2</v>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="P30" s="7" cm="1">
         <f t="array" ref="P30">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>5.2631578947368418E-2</v>
+        <v>5.3571428571428568E-2</v>
       </c>
       <c r="Q30" s="7"/>
     </row>
@@ -1836,24 +1809,24 @@
         <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D31" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f>F23/2</f>
+        <v>1</v>
       </c>
       <c r="F31" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="0"/>
+        <f>D28/I31</f>
         <v>0.25</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" si="10"/>
+        <f>SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
       <c r="J31" s="3" t="s">
@@ -1877,11 +1850,11 @@
       </c>
       <c r="O31" s="7" cm="1">
         <f t="array" ref="O31">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>3.3898305084745763E-2</v>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="P31" s="7" cm="1">
         <f t="array" ref="P31">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>3.5087719298245612E-2</v>
+        <v>3.5714285714285712E-2</v>
       </c>
       <c r="Q31" s="7"/>
     </row>
@@ -1893,25 +1866,24 @@
         <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D32" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="9"/>
-        <v>0.04</v>
+        <f>F24/2</f>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <f>F23*2</f>
-        <v>0.16</v>
+        <v>2</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="0"/>
+        <f>D29/I32</f>
         <v>0.1875</v>
       </c>
       <c r="I32" s="3">
-        <f t="shared" si="10"/>
+        <f>SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -1935,11 +1907,11 @@
       </c>
       <c r="O32" s="7" cm="1">
         <f t="array" ref="O32">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>1.6949152542372881E-2</v>
+        <v>1.7241379310344827E-2</v>
       </c>
       <c r="P32" s="7" cm="1">
         <f t="array" ref="P32">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>1.7543859649122806E-2</v>
+        <v>1.7857142857142856E-2</v>
       </c>
       <c r="Q32" s="7"/>
     </row>
@@ -1951,53 +1923,31 @@
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D33" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="9"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="0"/>
+        <f>D30/I33</f>
         <v>6.25E-2</v>
       </c>
       <c r="I33" s="3">
-        <f t="shared" si="10"/>
+        <f>SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K33" s="7" cm="1">
-        <f t="array" ref="K33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="7" cm="1">
-        <f t="array" ref="L33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="7" cm="1">
-        <f t="array" ref="M33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="7" cm="1">
-        <f t="array" ref="N33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>0</v>
-      </c>
-      <c r="O33" s="7" cm="1">
-        <f t="array" ref="O33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>1.6949152542372881E-2</v>
-      </c>
-      <c r="P33" s="7" cm="1">
-        <f t="array" ref="P33">INDEX($H:$H, ROW($H$2) + (COLUMN()-COLUMN($K$25))*9 + (ROW()-ROW($K$25)))</f>
-        <v>1.7543859649122806E-2</v>
-      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
@@ -2005,27 +1955,28 @@
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D34" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E34" s="3">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <f>F26/2</f>
+        <v>64</v>
       </c>
       <c r="F34" s="3">
-        <v>4</v>
+        <f>F26*2</f>
+        <v>256</v>
       </c>
       <c r="H34" s="7">
-        <f t="shared" si="0"/>
+        <f>D31/I34</f>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="I34" s="3">
-        <f t="shared" si="10"/>
+        <f>SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
       <c r="K34" s="7"/>
@@ -2041,27 +1992,28 @@
         <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>F27/2</f>
+        <v>64</v>
       </c>
       <c r="F35" s="3">
-        <v>2</v>
+        <f>F27*2</f>
+        <v>256</v>
       </c>
       <c r="H35" s="7">
-        <f t="shared" si="0"/>
+        <f>D32/I35</f>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" si="10"/>
+        <f>SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
     </row>
@@ -2070,26 +2022,27 @@
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="1">
+        <v>12</v>
+      </c>
+      <c r="E36" s="3">
+        <f>F28/2</f>
+        <v>4</v>
+      </c>
+      <c r="F36" s="3">
         <v>10</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3">
-        <v>0</v>
-      </c>
       <c r="H36" s="7">
-        <f t="shared" si="0"/>
+        <f>D33/I36</f>
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <f t="shared" si="10"/>
+        <f>SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
     </row>
@@ -2098,28 +2051,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E37" s="3">
-        <v>0</v>
+        <f>F29/2</f>
+        <v>0.08</v>
       </c>
       <c r="F37" s="3">
-        <v>0</v>
-      </c>
-      <c r="H37" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="3">
-        <f t="shared" si="10"/>
-        <v>48</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="H37" s="7"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
@@ -2129,26 +2076,25 @@
         <v>12</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D38" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" ref="E38:E43" si="11">F29/2</f>
-        <v>64</v>
+        <f>F30/2</f>
+        <v>3</v>
       </c>
       <c r="F38" s="3">
-        <f>F29*2</f>
-        <v>256</v>
+        <v>8</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="0"/>
-        <v>0.20338983050847459</v>
+        <f>D34/I38</f>
+        <v>0.20689655172413793</v>
       </c>
       <c r="I38" s="3">
-        <f>SUM($D$38:$D$46)</f>
-        <v>59</v>
+        <f>SUM($D$34:$D$41)</f>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
@@ -2159,26 +2105,26 @@
         <v>12</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D39" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E39" s="3">
-        <f t="shared" si="11"/>
-        <v>64</v>
+        <f>F31/2</f>
+        <v>2</v>
       </c>
       <c r="F39" s="3">
-        <f>F30*2</f>
-        <v>256</v>
+        <f>F31*2</f>
+        <v>8</v>
       </c>
       <c r="H39" s="7">
-        <f t="shared" si="0"/>
-        <v>0.20338983050847459</v>
+        <f>D35/I39</f>
+        <v>0.20689655172413793</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" ref="I39:I46" si="12">SUM($D$38:$D$46)</f>
-        <v>59</v>
+        <f>SUM($D$34:$D$41)</f>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
@@ -2189,25 +2135,24 @@
         <v>12</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D40" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E40" s="3">
-        <f t="shared" si="11"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F40" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H40" s="7">
-        <f t="shared" si="0"/>
-        <v>0.20338983050847459</v>
+        <f>D36/I40</f>
+        <v>0.20689655172413793</v>
       </c>
       <c r="I40" s="3">
-        <f t="shared" si="12"/>
-        <v>59</v>
+        <f>SUM($D$34:$D$41)</f>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
@@ -2218,25 +2163,24 @@
         <v>12</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D41" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E41" s="3">
-        <f t="shared" si="11"/>
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="H41" s="7">
-        <f t="shared" si="0"/>
-        <v>0.20338983050847459</v>
+        <f>D37/I41</f>
+        <v>0.20689655172413793</v>
       </c>
       <c r="I41" s="3">
-        <f t="shared" si="12"/>
-        <v>59</v>
+        <f>SUM($D$34:$D$41)</f>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
@@ -2244,28 +2188,28 @@
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="1">
         <v>12</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42" s="1">
-        <v>4</v>
-      </c>
       <c r="E42" s="3">
-        <f t="shared" si="11"/>
-        <v>3</v>
+        <f>F34/2</f>
+        <v>128</v>
       </c>
       <c r="F42" s="3">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="0"/>
-        <v>6.7796610169491525E-2</v>
+        <f>D38/I42</f>
+        <v>6.8965517241379309E-2</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" si="12"/>
-        <v>59</v>
+        <f>SUM($D$34:$D$41)</f>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
@@ -2273,29 +2217,28 @@
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D43" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E43" s="3">
-        <f t="shared" si="11"/>
-        <v>2</v>
+        <f>F35/2</f>
+        <v>128</v>
       </c>
       <c r="F43" s="3">
-        <f>F34*2</f>
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="H43" s="7">
-        <f t="shared" si="0"/>
-        <v>5.0847457627118647E-2</v>
+        <f>D39/I43</f>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="I43" s="3">
-        <f t="shared" si="12"/>
-        <v>59</v>
+        <f>SUM($D$34:$D$41)</f>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
@@ -2303,27 +2246,29 @@
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D44" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E44" s="3">
-        <v>1</v>
+        <f>F36/2</f>
+        <v>5</v>
       </c>
       <c r="F44" s="3">
-        <v>6</v>
+        <f>F36*2</f>
+        <v>20</v>
       </c>
       <c r="H44" s="7">
-        <f t="shared" si="0"/>
-        <v>3.3898305084745763E-2</v>
+        <f>D40/I44</f>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="I44" s="3">
-        <f t="shared" si="12"/>
-        <v>59</v>
+        <f>SUM($D$34:$D$41)</f>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
@@ -2331,27 +2276,29 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="1">
         <v>12</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D45" s="1">
-        <v>1</v>
-      </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <f>F37/2</f>
+        <v>0.1</v>
       </c>
       <c r="F45" s="3">
-        <v>4</v>
+        <f>F37*2</f>
+        <v>0.4</v>
       </c>
       <c r="H45" s="7">
-        <f t="shared" si="0"/>
-        <v>1.6949152542372881E-2</v>
+        <f>D41/I45</f>
+        <v>1.7241379310344827E-2</v>
       </c>
       <c r="I45" s="3">
-        <f t="shared" si="12"/>
-        <v>59</v>
+        <f>SUM($D$34:$D$41)</f>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
@@ -2359,28 +2306,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <f>F38/2</f>
+        <v>4</v>
       </c>
       <c r="F46" s="3">
-        <v>4</v>
-      </c>
-      <c r="H46" s="7">
-        <f t="shared" si="0"/>
-        <v>1.6949152542372881E-2</v>
-      </c>
-      <c r="I46" s="3">
-        <f t="shared" si="12"/>
-        <v>59</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
@@ -2390,25 +2331,25 @@
         <v>14</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D47" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E47" s="3">
-        <f t="shared" ref="E47:E53" si="13">F38/2</f>
-        <v>128</v>
+        <f>F39/2</f>
+        <v>4</v>
       </c>
       <c r="F47" s="3">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="H47" s="7">
-        <f t="shared" si="0"/>
-        <v>0.21052631578947367</v>
+        <f>D42/I47</f>
+        <v>0.21428571428571427</v>
       </c>
       <c r="I47" s="3">
-        <f>SUM($D$47:$D$55)</f>
-        <v>57</v>
+        <f>SUM($D$42:$D$55)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
@@ -2419,25 +2360,25 @@
         <v>14</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E48" s="3">
-        <f t="shared" si="13"/>
-        <v>128</v>
+        <f>F40/2</f>
+        <v>3</v>
       </c>
       <c r="F48" s="3">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="H48" s="7">
-        <f t="shared" si="0"/>
-        <v>0.19298245614035087</v>
+        <f>D43/I48</f>
+        <v>0.19642857142857142</v>
       </c>
       <c r="I48" s="3">
-        <f t="shared" ref="I48:I55" si="14">SUM($D$47:$D$55)</f>
-        <v>57</v>
+        <f>SUM($D$42:$D$55)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
@@ -2448,200 +2389,89 @@
         <v>14</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D49" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E49" s="3">
-        <f t="shared" si="13"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F49" s="3">
-        <f t="shared" ref="F49:F50" si="15">F40*2</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="0"/>
-        <v>0.19298245614035087</v>
+        <f>D44/I49</f>
+        <v>0.19642857142857142</v>
       </c>
       <c r="I49" s="3">
-        <f t="shared" si="14"/>
-        <v>57</v>
+        <f>SUM($D$42:$D$55)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
-        <v>48</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="1">
-        <v>12</v>
-      </c>
-      <c r="E50" s="3">
-        <f t="shared" si="13"/>
-        <v>0.1</v>
-      </c>
-      <c r="F50" s="3">
-        <f t="shared" si="15"/>
-        <v>0.4</v>
-      </c>
+      <c r="A50" s="1"/>
       <c r="H50" s="7">
-        <f t="shared" si="0"/>
-        <v>0.21052631578947367</v>
+        <f>D45/I50</f>
+        <v>0.21428571428571427</v>
       </c>
       <c r="I50" s="3">
-        <f t="shared" si="14"/>
-        <v>57</v>
+        <f>SUM($D$42:$D$55)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
-        <v>49</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D51" s="1">
-        <v>4</v>
-      </c>
-      <c r="E51" s="3">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="F51" s="3">
-        <v>10</v>
-      </c>
+      <c r="A51" s="1"/>
       <c r="H51" s="7">
-        <f t="shared" si="0"/>
-        <v>7.0175438596491224E-2</v>
+        <f>D46/I51</f>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" si="14"/>
-        <v>57</v>
+        <f>SUM($D$42:$D$55)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
-        <v>50</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D52" s="1">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="F52" s="3">
-        <v>10</v>
-      </c>
+      <c r="A52" s="1"/>
       <c r="H52" s="7">
-        <f t="shared" si="0"/>
-        <v>5.2631578947368418E-2</v>
+        <f>D47/I52</f>
+        <v>5.3571428571428568E-2</v>
       </c>
       <c r="I52" s="3">
-        <f t="shared" si="14"/>
-        <v>57</v>
+        <f>SUM($D$42:$D$55)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
-        <v>51</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="1">
-        <v>2</v>
-      </c>
-      <c r="E53" s="3">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="F53" s="3">
-        <v>10</v>
-      </c>
+      <c r="A53" s="1"/>
       <c r="H53" s="7">
-        <f t="shared" si="0"/>
-        <v>3.5087719298245612E-2</v>
+        <f>D48/I53</f>
+        <v>3.5714285714285712E-2</v>
       </c>
       <c r="I53" s="3">
-        <f t="shared" si="14"/>
-        <v>57</v>
+        <f>SUM($D$42:$D$55)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
-        <v>52</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="1">
-        <v>1</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3">
-        <v>8</v>
-      </c>
+      <c r="A54" s="1"/>
       <c r="H54" s="7">
-        <f t="shared" si="0"/>
-        <v>1.7543859649122806E-2</v>
+        <f>D49/I54</f>
+        <v>1.7857142857142856E-2</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" si="14"/>
-        <v>57</v>
+        <f>SUM($D$42:$D$55)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
-        <v>53</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D55" s="1">
-        <v>1</v>
-      </c>
-      <c r="E55" s="3">
-        <v>1</v>
-      </c>
-      <c r="F55" s="3">
-        <v>8</v>
-      </c>
-      <c r="H55" s="7">
-        <f t="shared" si="0"/>
-        <v>1.7543859649122806E-2</v>
-      </c>
-      <c r="I55" s="3">
-        <f t="shared" si="14"/>
-        <v>57</v>
-      </c>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="H55" s="7"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
@@ -3477,10 +3307,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B55" xr:uid="{6F7C22CB-3302-4FCE-BE29-634B012439FF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B49 B55" xr:uid="{6F7C22CB-3302-4FCE-BE29-634B012439FF}">
       <formula1>$L$2:$L$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C55" xr:uid="{061ACE8B-28B7-46EA-8228-C23E0DB18982}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C49 C55" xr:uid="{061ACE8B-28B7-46EA-8228-C23E0DB18982}">
       <formula1>$K$2:$K$10</formula1>
     </dataValidation>
   </dataValidations>

--- a/Assets/AddressableResource/Data/Excels/TowerWeaponJewelData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/TowerWeaponJewelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D799CC7-582B-493C-91FD-9B4BEEF6BB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0017524-C7A9-4CEF-B21F-767158E88424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -687,7 +687,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="7">
-        <f t="shared" ref="H2:H55" si="0">D2/I2</f>
+        <f t="shared" ref="H2:H8" si="0">D2/I2</f>
         <v>6.5217391304347824E-2</v>
       </c>
       <c r="I2" s="3">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H5" s="7">
         <f t="shared" si="0"/>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" ref="H9:H10" si="2">D9/I9</f>
+        <f t="shared" ref="H9" si="2">D9/I9</f>
         <v>0</v>
       </c>
       <c r="I9" s="3">
@@ -947,12 +947,11 @@
         <v>5</v>
       </c>
       <c r="E10" s="3">
-        <f>F2/2</f>
+        <f t="shared" ref="E10:E16" si="3">F2/2</f>
         <v>8</v>
       </c>
       <c r="F10" s="3">
-        <f>F2*2</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -970,19 +969,18 @@
         <v>20</v>
       </c>
       <c r="E11" s="3">
-        <f>F3/2</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="F11" s="3">
-        <f>F3*2</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H11" s="7">
-        <f>D10/I11</f>
+        <f t="shared" ref="H11:H18" si="4">D10/I11</f>
         <v>9.8039215686274508E-2</v>
       </c>
       <c r="I11" s="3">
-        <f>SUM($D$10:$D$17)</f>
+        <f t="shared" ref="I11:I18" si="5">SUM($D$10:$D$17)</f>
         <v>51</v>
       </c>
     </row>
@@ -1000,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="3">
-        <f>F4/2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F12" s="3">
@@ -1008,11 +1006,11 @@
         <v>4</v>
       </c>
       <c r="H12" s="7">
-        <f>D11/I12</f>
+        <f t="shared" si="4"/>
         <v>0.39215686274509803</v>
       </c>
       <c r="I12" s="3">
-        <f>SUM($D$10:$D$17)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
     </row>
@@ -1030,19 +1028,19 @@
         <v>5</v>
       </c>
       <c r="E13" s="3">
-        <f>F5/2</f>
-        <v>0.01</v>
+        <f t="shared" si="3"/>
+        <v>0.05</v>
       </c>
       <c r="F13" s="3">
         <f>F5*2</f>
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="7">
-        <f>D12/I13</f>
+        <f t="shared" si="4"/>
         <v>0.39215686274509803</v>
       </c>
       <c r="I13" s="3">
-        <f>SUM($D$10:$D$17)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="J13" s="1">
@@ -1074,18 +1072,18 @@
         <v>1</v>
       </c>
       <c r="E14" s="3">
-        <f>F6/2</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F14" s="3">
         <v>2</v>
       </c>
       <c r="H14" s="7">
-        <f>D13/I14</f>
+        <f t="shared" si="4"/>
         <v>9.8039215686274508E-2</v>
       </c>
       <c r="I14" s="3">
-        <f>SUM($D$10:$D$17)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="J14" s="1">
@@ -1095,11 +1093,11 @@
         <v>3150</v>
       </c>
       <c r="L14" s="3">
-        <f t="shared" ref="L14" si="3">K14*2</f>
+        <f t="shared" ref="L14" si="6">K14*2</f>
         <v>6300</v>
       </c>
       <c r="M14">
-        <f t="shared" ref="M14:M17" si="4">K14/(J14/100)</f>
+        <f t="shared" ref="M14:M17" si="7">K14/(J14/100)</f>
         <v>315000</v>
       </c>
     </row>
@@ -1117,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <f>F7/2</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F15" s="3">
@@ -1125,11 +1123,11 @@
         <v>0</v>
       </c>
       <c r="H15" s="7">
-        <f>D14/I15</f>
+        <f t="shared" si="4"/>
         <v>1.9607843137254902E-2</v>
       </c>
       <c r="I15" s="3">
-        <f>SUM($D$10:$D$17)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="J15" s="1">
@@ -1143,7 +1141,7 @@
         <v>19860</v>
       </c>
       <c r="M15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>827500</v>
       </c>
     </row>
@@ -1161,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f>F8/2</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F16" s="3">
@@ -1169,11 +1167,11 @@
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <f>D15/I16</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I16" s="3">
-        <f>SUM($D$10:$D$17)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="J16" s="1">
@@ -1187,7 +1185,7 @@
         <v>41730</v>
       </c>
       <c r="M16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>2782000</v>
       </c>
     </row>
@@ -1211,11 +1209,11 @@
         <v>0</v>
       </c>
       <c r="H17" s="7">
-        <f>D16/I17</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <f>SUM($D$10:$D$17)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="J17" s="1">
@@ -1229,7 +1227,7 @@
         <v>116880</v>
       </c>
       <c r="M17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>9740000</v>
       </c>
     </row>
@@ -1247,19 +1245,18 @@
         <v>6</v>
       </c>
       <c r="E18" s="3">
-        <f>F10/2</f>
-        <v>16</v>
+        <f t="shared" ref="E18:E24" si="8">F10/2</f>
+        <v>15</v>
       </c>
       <c r="F18" s="3">
-        <f>F10*2</f>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H18" s="7">
-        <f>D17/I18</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <f>SUM($D$10:$D$17)</f>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="J18" s="1">
@@ -1287,12 +1284,11 @@
         <v>17</v>
       </c>
       <c r="E19" s="3">
-        <f>F11/2</f>
-        <v>16</v>
+        <f t="shared" si="8"/>
+        <v>15</v>
       </c>
       <c r="F19" s="3">
-        <f>F11*2</f>
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H19" s="7"/>
       <c r="J19" s="1"/>
@@ -1312,18 +1308,18 @@
         <v>17</v>
       </c>
       <c r="E20" s="3">
-        <f>F12/2</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="F20" s="3">
         <v>6</v>
       </c>
       <c r="H20" s="7">
-        <f>D18/I20</f>
+        <f t="shared" ref="H20:H27" si="9">D18/I20</f>
         <v>0.12244897959183673</v>
       </c>
       <c r="I20" s="3">
-        <f>SUM($D$18:$D$25)</f>
+        <f t="shared" ref="I20:I27" si="10">SUM($D$18:$D$25)</f>
         <v>49</v>
       </c>
     </row>
@@ -1341,19 +1337,18 @@
         <v>6</v>
       </c>
       <c r="E21" s="3">
-        <f>F13/2</f>
-        <v>0.02</v>
+        <f t="shared" si="8"/>
+        <v>0.1</v>
       </c>
       <c r="F21" s="3">
-        <f>F13*2</f>
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H21" s="7">
-        <f>D19/I21</f>
+        <f t="shared" si="9"/>
         <v>0.34693877551020408</v>
       </c>
       <c r="I21" s="3">
-        <f>SUM($D$18:$D$25)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="J21" s="7"/>
@@ -1372,18 +1367,18 @@
         <v>2</v>
       </c>
       <c r="E22" s="3">
-        <f>F14/2</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F22" s="3">
         <v>4</v>
       </c>
       <c r="H22" s="7">
-        <f>D20/I22</f>
+        <f t="shared" si="9"/>
         <v>0.34693877551020408</v>
       </c>
       <c r="I22" s="3">
-        <f>SUM($D$18:$D$25)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
     </row>
@@ -1401,18 +1396,18 @@
         <v>1</v>
       </c>
       <c r="E23" s="3">
-        <f>F15/2</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>2</v>
       </c>
       <c r="H23" s="7">
-        <f>D21/I23</f>
+        <f t="shared" si="9"/>
         <v>0.12244897959183673</v>
       </c>
       <c r="I23" s="3">
-        <f>SUM($D$18:$D$25)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
     </row>
@@ -1430,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <f>F16/2</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F24" s="3">
@@ -1438,11 +1433,11 @@
         <v>0</v>
       </c>
       <c r="H24" s="7">
-        <f>D22/I24</f>
+        <f t="shared" si="9"/>
         <v>4.0816326530612242E-2</v>
       </c>
       <c r="I24" s="3">
-        <f>SUM($D$18:$D$25)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="K24" s="3" t="s">
@@ -1484,11 +1479,11 @@
         <v>0</v>
       </c>
       <c r="H25" s="7">
-        <f>D23/I25</f>
+        <f t="shared" si="9"/>
         <v>2.0408163265306121E-2</v>
       </c>
       <c r="I25" s="3">
-        <f>SUM($D$18:$D$25)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="J25" s="3" t="s">
@@ -1534,19 +1529,18 @@
         <v>9</v>
       </c>
       <c r="E26" s="3">
-        <f>F18/2</f>
-        <v>32</v>
+        <f t="shared" ref="E26:E32" si="11">F18/2</f>
+        <v>30</v>
       </c>
       <c r="F26" s="3">
-        <f>F18*2</f>
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="H26" s="7">
-        <f>D24/I26</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <f>SUM($D$18:$D$25)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="J26" s="3" t="s">
@@ -1592,19 +1586,18 @@
         <v>12</v>
       </c>
       <c r="E27" s="3">
-        <f>F19/2</f>
-        <v>32</v>
+        <f t="shared" si="11"/>
+        <v>30</v>
       </c>
       <c r="F27" s="3">
-        <f>F19*2</f>
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="H27" s="7">
-        <f>D25/I27</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <f>SUM($D$18:$D$25)</f>
+        <f t="shared" si="10"/>
         <v>49</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -1650,7 +1643,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="3">
-        <f>F20/2</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="F28" s="3">
@@ -1700,19 +1693,18 @@
         <v>9</v>
       </c>
       <c r="E29" s="3">
-        <f>F21/2</f>
-        <v>0.04</v>
+        <f t="shared" si="11"/>
+        <v>0.1</v>
       </c>
       <c r="F29" s="3">
-        <f>F21*2</f>
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="H29" s="7">
-        <f>D26/I29</f>
+        <f t="shared" ref="H29:H36" si="12">D26/I29</f>
         <v>0.1875</v>
       </c>
       <c r="I29" s="3">
-        <f>SUM($D$26:$D$33)</f>
+        <f t="shared" ref="I29:I36" si="13">SUM($D$26:$D$33)</f>
         <v>48</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -1758,18 +1750,18 @@
         <v>3</v>
       </c>
       <c r="E30" s="3">
-        <f>F22/2</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="F30" s="3">
         <v>6</v>
       </c>
       <c r="H30" s="7">
-        <f>D27/I30</f>
+        <f t="shared" si="12"/>
         <v>0.25</v>
       </c>
       <c r="I30" s="3">
-        <f>SUM($D$26:$D$33)</f>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -1815,18 +1807,18 @@
         <v>2</v>
       </c>
       <c r="E31" s="3">
-        <f>F23/2</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="F31" s="3">
         <v>4</v>
       </c>
       <c r="H31" s="7">
-        <f>D28/I31</f>
+        <f t="shared" si="12"/>
         <v>0.25</v>
       </c>
       <c r="I31" s="3">
-        <f>SUM($D$26:$D$33)</f>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="J31" s="3" t="s">
@@ -1872,18 +1864,18 @@
         <v>1</v>
       </c>
       <c r="E32" s="3">
-        <f>F24/2</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>2</v>
       </c>
       <c r="H32" s="7">
-        <f>D29/I32</f>
+        <f t="shared" si="12"/>
         <v>0.1875</v>
       </c>
       <c r="I32" s="3">
-        <f>SUM($D$26:$D$33)</f>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -1935,11 +1927,11 @@
         <v>0</v>
       </c>
       <c r="H33" s="7">
-        <f>D30/I33</f>
+        <f t="shared" si="12"/>
         <v>6.25E-2</v>
       </c>
       <c r="I33" s="3">
-        <f>SUM($D$26:$D$33)</f>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="K33" s="7"/>
@@ -1964,19 +1956,18 @@
         <v>12</v>
       </c>
       <c r="E34" s="3">
-        <f>F26/2</f>
-        <v>64</v>
+        <f t="shared" ref="E34:E39" si="14">F26/2</f>
+        <v>45</v>
       </c>
       <c r="F34" s="3">
-        <f>F26*2</f>
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="H34" s="7">
-        <f>D31/I34</f>
+        <f t="shared" si="12"/>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="I34" s="3">
-        <f>SUM($D$26:$D$33)</f>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
       <c r="K34" s="7"/>
@@ -2001,19 +1992,18 @@
         <v>12</v>
       </c>
       <c r="E35" s="3">
-        <f>F27/2</f>
-        <v>64</v>
+        <f t="shared" si="14"/>
+        <v>45</v>
       </c>
       <c r="F35" s="3">
-        <f>F27*2</f>
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="H35" s="7">
-        <f>D32/I35</f>
+        <f t="shared" si="12"/>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="I35" s="3">
-        <f>SUM($D$26:$D$33)</f>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
     </row>
@@ -2031,18 +2021,18 @@
         <v>12</v>
       </c>
       <c r="E36" s="3">
-        <f>F28/2</f>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="F36" s="3">
         <v>10</v>
       </c>
       <c r="H36" s="7">
-        <f>D33/I36</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <f>SUM($D$26:$D$33)</f>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
     </row>
@@ -2060,11 +2050,11 @@
         <v>12</v>
       </c>
       <c r="E37" s="3">
-        <f>F29/2</f>
-        <v>0.08</v>
+        <f t="shared" si="14"/>
+        <v>0.3</v>
       </c>
       <c r="F37" s="3">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="7"/>
     </row>
@@ -2082,18 +2072,18 @@
         <v>4</v>
       </c>
       <c r="E38" s="3">
-        <f>F30/2</f>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="F38" s="3">
         <v>8</v>
       </c>
       <c r="H38" s="7">
-        <f>D34/I38</f>
+        <f t="shared" ref="H38:H45" si="15">D34/I38</f>
         <v>0.20689655172413793</v>
       </c>
       <c r="I38" s="3">
-        <f>SUM($D$34:$D$41)</f>
+        <f t="shared" ref="I38:I45" si="16">SUM($D$34:$D$41)</f>
         <v>58</v>
       </c>
     </row>
@@ -2111,19 +2101,18 @@
         <v>3</v>
       </c>
       <c r="E39" s="3">
-        <f>F31/2</f>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="F39" s="3">
-        <f>F31*2</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H39" s="7">
-        <f>D35/I39</f>
+        <f t="shared" si="15"/>
         <v>0.20689655172413793</v>
       </c>
       <c r="I39" s="3">
-        <f>SUM($D$34:$D$41)</f>
+        <f t="shared" si="16"/>
         <v>58</v>
       </c>
     </row>
@@ -2144,14 +2133,14 @@
         <v>1</v>
       </c>
       <c r="F40" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H40" s="7">
-        <f>D36/I40</f>
+        <f t="shared" si="15"/>
         <v>0.20689655172413793</v>
       </c>
       <c r="I40" s="3">
-        <f>SUM($D$34:$D$41)</f>
+        <f t="shared" si="16"/>
         <v>58</v>
       </c>
     </row>
@@ -2172,14 +2161,14 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H41" s="7">
-        <f>D37/I41</f>
+        <f t="shared" si="15"/>
         <v>0.20689655172413793</v>
       </c>
       <c r="I41" s="3">
-        <f>SUM($D$34:$D$41)</f>
+        <f t="shared" si="16"/>
         <v>58</v>
       </c>
     </row>
@@ -2197,18 +2186,18 @@
         <v>12</v>
       </c>
       <c r="E42" s="3">
-        <f>F34/2</f>
-        <v>128</v>
+        <f t="shared" ref="E42:E48" si="17">F34/2</f>
+        <v>90</v>
       </c>
       <c r="F42" s="3">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H42" s="7">
-        <f>D38/I42</f>
+        <f t="shared" si="15"/>
         <v>6.8965517241379309E-2</v>
       </c>
       <c r="I42" s="3">
-        <f>SUM($D$34:$D$41)</f>
+        <f t="shared" si="16"/>
         <v>58</v>
       </c>
     </row>
@@ -2226,18 +2215,18 @@
         <v>11</v>
       </c>
       <c r="E43" s="3">
-        <f>F35/2</f>
-        <v>128</v>
+        <f t="shared" si="17"/>
+        <v>90</v>
       </c>
       <c r="F43" s="3">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H43" s="7">
-        <f>D39/I43</f>
+        <f t="shared" si="15"/>
         <v>5.1724137931034482E-2</v>
       </c>
       <c r="I43" s="3">
-        <f>SUM($D$34:$D$41)</f>
+        <f t="shared" si="16"/>
         <v>58</v>
       </c>
     </row>
@@ -2255,7 +2244,7 @@
         <v>11</v>
       </c>
       <c r="E44" s="3">
-        <f>F36/2</f>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="F44" s="3">
@@ -2263,11 +2252,11 @@
         <v>20</v>
       </c>
       <c r="H44" s="7">
-        <f>D40/I44</f>
+        <f t="shared" si="15"/>
         <v>3.4482758620689655E-2</v>
       </c>
       <c r="I44" s="3">
-        <f>SUM($D$34:$D$41)</f>
+        <f t="shared" si="16"/>
         <v>58</v>
       </c>
     </row>
@@ -2285,19 +2274,18 @@
         <v>12</v>
       </c>
       <c r="E45" s="3">
-        <f>F37/2</f>
-        <v>0.1</v>
+        <f t="shared" si="17"/>
+        <v>0.5</v>
       </c>
       <c r="F45" s="3">
-        <f>F37*2</f>
-        <v>0.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H45" s="7">
-        <f>D41/I45</f>
+        <f t="shared" si="15"/>
         <v>1.7241379310344827E-2</v>
       </c>
       <c r="I45" s="3">
-        <f>SUM($D$34:$D$41)</f>
+        <f t="shared" si="16"/>
         <v>58</v>
       </c>
     </row>
@@ -2315,11 +2303,11 @@
         <v>4</v>
       </c>
       <c r="E46" s="3">
-        <f>F38/2</f>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="F46" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H46" s="7"/>
     </row>
@@ -2337,18 +2325,17 @@
         <v>3</v>
       </c>
       <c r="E47" s="3">
-        <f>F39/2</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H47" s="7">
-        <f>D42/I47</f>
+        <f t="shared" ref="H47:H54" si="18">D42/I47</f>
         <v>0.21428571428571427</v>
       </c>
       <c r="I47" s="3">
-        <f>SUM($D$42:$D$55)</f>
+        <f t="shared" ref="I47:I54" si="19">SUM($D$42:$D$55)</f>
         <v>56</v>
       </c>
     </row>
@@ -2366,18 +2353,17 @@
         <v>2</v>
       </c>
       <c r="E48" s="3">
-        <f>F40/2</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" s="3">
-        <v>10</v>
+        <v>24.5</v>
       </c>
       <c r="H48" s="7">
-        <f>D43/I48</f>
+        <f t="shared" si="18"/>
         <v>0.19642857142857142</v>
       </c>
       <c r="I48" s="3">
-        <f>SUM($D$42:$D$55)</f>
+        <f t="shared" si="19"/>
         <v>56</v>
       </c>
     </row>
@@ -2398,69 +2384,69 @@
         <v>1</v>
       </c>
       <c r="F49" s="3">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H49" s="7">
-        <f>D44/I49</f>
+        <f t="shared" si="18"/>
         <v>0.19642857142857142</v>
       </c>
       <c r="I49" s="3">
-        <f>SUM($D$42:$D$55)</f>
+        <f t="shared" si="19"/>
         <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="H50" s="7">
-        <f>D45/I50</f>
+        <f t="shared" si="18"/>
         <v>0.21428571428571427</v>
       </c>
       <c r="I50" s="3">
-        <f>SUM($D$42:$D$55)</f>
+        <f t="shared" si="19"/>
         <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="H51" s="7">
-        <f>D46/I51</f>
+        <f t="shared" si="18"/>
         <v>7.1428571428571425E-2</v>
       </c>
       <c r="I51" s="3">
-        <f>SUM($D$42:$D$55)</f>
+        <f t="shared" si="19"/>
         <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="H52" s="7">
-        <f>D47/I52</f>
+        <f t="shared" si="18"/>
         <v>5.3571428571428568E-2</v>
       </c>
       <c r="I52" s="3">
-        <f>SUM($D$42:$D$55)</f>
+        <f t="shared" si="19"/>
         <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="H53" s="7">
-        <f>D48/I53</f>
+        <f t="shared" si="18"/>
         <v>3.5714285714285712E-2</v>
       </c>
       <c r="I53" s="3">
-        <f>SUM($D$42:$D$55)</f>
+        <f t="shared" si="19"/>
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="H54" s="7">
-        <f>D49/I54</f>
+        <f t="shared" si="18"/>
         <v>1.7857142857142856E-2</v>
       </c>
       <c r="I54" s="3">
-        <f>SUM($D$42:$D$55)</f>
+        <f t="shared" si="19"/>
         <v>56</v>
       </c>
     </row>
